--- a/Deliverables/SM_Bottom Board/_BOM/SM_Bottom_Board_DigiKey.xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/SM_Bottom_Board_DigiKey.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0FAFA8-D593-4D57-B250-FE6A067A5339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-5085" yWindow="7680" windowWidth="10335" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SM_Bottom_Board" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">SM_Bottom_Board!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="184">
   <si>
     <t>Description</t>
   </si>
@@ -281,27 +282,9 @@
     <t>RC0603FR-07470RL</t>
   </si>
   <si>
-    <t>Res SMD 0603 46.4 Ohm 1% 1/10W</t>
-  </si>
-  <si>
     <t>R7, R8</t>
   </si>
   <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>ERJ-3EKF46R4V</t>
-  </si>
-  <si>
-    <t>RES SMD 1K OHM 1% 1/20W 0201</t>
-  </si>
-  <si>
-    <t>R9, R10</t>
-  </si>
-  <si>
-    <t>RC0201FR-071KL</t>
-  </si>
-  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
@@ -522,9 +505,6 @@
   </si>
   <si>
     <t>Single Board Cost</t>
-  </si>
-  <si>
-    <t>C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C15, C20, C32, C33, C34, C35, C36, C37, C50, CF1</t>
   </si>
   <si>
     <t xml:space="preserve">Custom </t>
@@ -576,9 +556,6 @@
 </t>
   </si>
   <si>
-    <t>46.4R</t>
-  </si>
-  <si>
     <t>Unit Cost (25 Boards)</t>
   </si>
   <si>
@@ -601,12 +578,21 @@
   </si>
   <si>
     <t>--</t>
+  </si>
+  <si>
+    <t>C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C15, C20, C32, C33, C34, C35, C36, C37, C50,CF1</t>
+  </si>
+  <si>
+    <t>RES SMD 57.6 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-0757R6L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
@@ -1018,7 +1004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1034,12 +1020,180 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1049,179 +1203,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1502,11 +1491,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
@@ -1529,41 +1518,41 @@
     <col min="19" max="19" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.42578125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="11"/>
+      <c r="A1" s="65" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>0</v>
@@ -1572,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>3</v>
@@ -1581,2308 +1570,2197 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="R2" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="56" t="s">
+      <c r="B3" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="9">
         <v>1</v>
       </c>
-      <c r="K3" s="14">
-        <f>J3*5</f>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K31" si="0">J3*5</f>
         <v>5</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="9">
         <f>J3*25</f>
         <v>25</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="9">
         <f>J3*100</f>
         <v>100</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="10">
         <v>0.31</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="10">
         <f>N3*J3</f>
         <v>0.31</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="10">
         <v>0.31</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="10">
         <f>P3*K3</f>
         <v>1.55</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="10">
         <v>0.21299999999999999</v>
       </c>
-      <c r="S3" s="54">
+      <c r="S3" s="49">
         <f>R3*L3</f>
         <v>5.3250000000000002</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="10">
         <v>0.12039999999999999</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="49">
         <f>T3*M3</f>
         <v>12.04</v>
       </c>
-      <c r="V3" s="37"/>
+      <c r="V3" s="32"/>
     </row>
-    <row r="4" spans="1:22" s="33" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" s="28" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="B4" s="68"/>
+      <c r="C4" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" s="16" t="s">
+      <c r="H4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="26">
         <v>20</v>
       </c>
-      <c r="K4" s="31">
-        <f>J4*5</f>
+      <c r="K4" s="26">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="L4" s="18">
-        <f t="shared" ref="L4:L32" si="0">J4*25</f>
+      <c r="L4" s="13">
+        <f t="shared" ref="L4:L31" si="1">J4*25</f>
         <v>500</v>
       </c>
-      <c r="M4" s="18">
-        <f t="shared" ref="M4:M32" si="1">J4*100</f>
+      <c r="M4" s="13">
+        <f t="shared" ref="M4:M31" si="2">J4*100</f>
         <v>2000</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="27">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="27">
         <f>N4*J4</f>
         <v>0.96</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="27">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="27">
         <f>P4*K4</f>
         <v>2.1399999999999997</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="27">
         <v>1.5259999999999999E-2</v>
       </c>
-      <c r="S4" s="42">
+      <c r="S4" s="37">
         <f>R4*L4</f>
         <v>7.63</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="27">
         <v>1.1990000000000001E-2</v>
       </c>
-      <c r="U4" s="42">
+      <c r="U4" s="37">
         <f>T4*M4</f>
         <v>23.98</v>
       </c>
-      <c r="V4" s="38"/>
+      <c r="V4" s="33"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="58" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F5" s="17" t="s">
+      <c r="E5" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="H5" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="13">
         <v>1</v>
       </c>
-      <c r="K5" s="18">
-        <f>J5*5</f>
+      <c r="K5" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="18">
-        <f t="shared" si="0"/>
+      <c r="L5" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M5" s="18">
-        <f t="shared" si="1"/>
+      <c r="M5" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="14">
         <v>0.79</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="14">
         <f>N5*J5</f>
         <v>0.79</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="14">
         <v>0.79</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="14">
         <f>P5*K5</f>
         <v>3.95</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="14">
         <v>0.55800000000000005</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="37">
         <f>R5*L5</f>
         <v>13.950000000000001</v>
       </c>
-      <c r="T5" s="19">
+      <c r="T5" s="14">
         <v>0.36770000000000003</v>
       </c>
-      <c r="U5" s="42">
+      <c r="U5" s="37">
         <f>T5*M5</f>
         <v>36.770000000000003</v>
       </c>
-      <c r="V5" s="39"/>
+      <c r="V5" s="34"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="H6" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="13">
         <v>2</v>
       </c>
-      <c r="K6" s="18">
-        <f>J6*5</f>
+      <c r="K6" s="13">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L6" s="18">
-        <f t="shared" si="0"/>
+      <c r="L6" s="13">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M6" s="18">
-        <f t="shared" si="1"/>
+      <c r="M6" s="13">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="14">
         <v>0.21</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="14">
         <f>N6*J6</f>
         <v>0.42</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="14">
         <v>0.14299999999999999</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="14">
         <f>P6*K6</f>
         <v>1.43</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="14">
         <v>8.5599999999999996E-2</v>
       </c>
-      <c r="S6" s="42">
+      <c r="S6" s="37">
         <f>R6*L6</f>
         <v>4.2799999999999994</v>
       </c>
-      <c r="T6" s="19">
+      <c r="T6" s="14">
         <v>7.2400000000000006E-2</v>
       </c>
-      <c r="U6" s="42">
+      <c r="U6" s="37">
         <f>T6*M6</f>
         <v>14.48</v>
       </c>
-      <c r="V6" s="39"/>
+      <c r="V6" s="34"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="H7" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="13">
         <v>4</v>
       </c>
-      <c r="K7" s="18">
-        <f>J7*5</f>
+      <c r="K7" s="13">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L7" s="18">
-        <f t="shared" si="0"/>
+      <c r="L7" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M7" s="18">
-        <f t="shared" si="1"/>
+      <c r="M7" s="13">
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="14">
         <v>0.11</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="14">
         <f>N7*J7</f>
         <v>0.44</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="14">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="14">
         <f>P7*K7</f>
         <v>1.58</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="14">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="S7" s="42">
+      <c r="S7" s="37">
         <f>R7*L7</f>
         <v>3.54</v>
       </c>
-      <c r="T7" s="19">
+      <c r="T7" s="14">
         <v>3.5400000000000001E-2</v>
       </c>
-      <c r="U7" s="42">
+      <c r="U7" s="37">
         <f>T7*M7</f>
         <v>14.16</v>
       </c>
-      <c r="V7" s="39"/>
+      <c r="V7" s="34"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="59" t="s">
+      <c r="B8" s="64"/>
+      <c r="C8" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="21">
+      <c r="H8" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="16">
         <v>1</v>
       </c>
-      <c r="K8" s="21">
-        <f>J8*5</f>
+      <c r="K8" s="16">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L8" s="21">
-        <f t="shared" si="0"/>
+      <c r="L8" s="16">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M8" s="21">
-        <f t="shared" si="1"/>
+      <c r="M8" s="16">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N8" s="22">
+      <c r="N8" s="17">
         <v>0.35</v>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="17">
         <f>N8*J8</f>
         <v>0.35</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="17">
         <v>0.35</v>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="17">
         <f>P8*K8</f>
         <v>1.75</v>
       </c>
-      <c r="R8" s="22">
+      <c r="R8" s="17">
         <v>0.24199999999999999</v>
       </c>
-      <c r="S8" s="55">
+      <c r="S8" s="50">
         <f>R8*L8</f>
         <v>6.05</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="17">
         <v>0.1368</v>
       </c>
-      <c r="U8" s="55">
+      <c r="U8" s="50">
         <f>T8*M8</f>
         <v>13.68</v>
       </c>
-      <c r="V8" s="40"/>
+      <c r="V8" s="35"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="56" t="s">
+      <c r="B9" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="J9" s="14">
+      <c r="H9" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="9">
         <v>2</v>
       </c>
-      <c r="K9" s="14">
-        <f>J9*5</f>
+      <c r="K9" s="9">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L9" s="14">
-        <f t="shared" si="0"/>
+      <c r="L9" s="9">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M9" s="14">
-        <f t="shared" si="1"/>
+      <c r="M9" s="9">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="18">
         <v>0.13100000000000001</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="10">
         <f>N9*J9</f>
         <v>0.26200000000000001</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="18">
         <v>0.13100000000000001</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="10">
         <f>P9*K9</f>
         <v>1.31</v>
       </c>
-      <c r="R9" s="15">
+      <c r="R9" s="10">
         <v>0.1048</v>
       </c>
-      <c r="S9" s="54">
+      <c r="S9" s="49">
         <f>R9*L9</f>
         <v>5.24</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="10">
         <v>0.1</v>
       </c>
-      <c r="U9" s="54">
+      <c r="U9" s="49">
         <f>T9*M9</f>
         <v>20</v>
       </c>
-      <c r="V9" s="68" t="s">
-        <v>161</v>
+      <c r="V9" s="59" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="58" t="s">
+      <c r="B10" s="68"/>
+      <c r="C10" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J10" s="18">
+      <c r="H10" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="13">
         <v>1</v>
       </c>
-      <c r="K10" s="18">
-        <f>J10*5</f>
+      <c r="K10" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="18">
-        <f t="shared" si="0"/>
+      <c r="L10" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M10" s="18">
-        <f t="shared" si="1"/>
+      <c r="M10" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="14">
         <v>0.38</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="14">
         <f>N10*J10</f>
         <v>0.38</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="14">
         <v>0.38</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="14">
         <f>P10*K10</f>
         <v>1.9</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="14">
         <v>0.28499999999999998</v>
       </c>
-      <c r="S10" s="42">
+      <c r="S10" s="37">
         <f>R10*L10</f>
         <v>7.1249999999999991</v>
       </c>
-      <c r="T10" s="19">
+      <c r="T10" s="14">
         <v>0.1613</v>
       </c>
-      <c r="U10" s="42">
+      <c r="U10" s="37">
         <f>T10*M10</f>
         <v>16.13</v>
       </c>
-      <c r="V10" s="39"/>
+      <c r="V10" s="34"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="64"/>
+      <c r="C11" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="J11" s="21">
+      <c r="H11" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J11" s="16">
         <v>1</v>
       </c>
-      <c r="K11" s="21">
-        <f>J11*5</f>
+      <c r="K11" s="16">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L11" s="21">
-        <f t="shared" si="0"/>
+      <c r="L11" s="16">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M11" s="21">
-        <f t="shared" si="1"/>
+      <c r="M11" s="16">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="17">
         <v>0.37</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="17">
         <f>N11*J11</f>
         <v>0.37</v>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="17">
         <v>0.37</v>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11" s="17">
         <f>P11*K11</f>
         <v>1.85</v>
       </c>
-      <c r="R11" s="22">
+      <c r="R11" s="17">
         <v>0.29299999999999998</v>
       </c>
-      <c r="S11" s="55">
+      <c r="S11" s="50">
         <f>R11*L11</f>
         <v>7.3249999999999993</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="17">
         <v>0.13139999999999999</v>
       </c>
-      <c r="U11" s="55">
+      <c r="U11" s="50">
         <f>T11*M11</f>
         <v>13.139999999999999</v>
       </c>
-      <c r="V11" s="40"/>
+      <c r="V11" s="35"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25">
+      <c r="H12" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20">
         <v>1</v>
       </c>
-      <c r="K12" s="25">
-        <f>J12*5</f>
+      <c r="K12" s="20">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L12" s="25">
-        <f t="shared" si="0"/>
+      <c r="L12" s="20">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M12" s="25">
-        <f t="shared" si="1"/>
+      <c r="M12" s="20">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="21">
         <v>0.192</v>
       </c>
-      <c r="O12" s="27">
+      <c r="O12" s="22">
         <f>N12*J12</f>
         <v>0.192</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="21">
         <v>0.192</v>
       </c>
-      <c r="Q12" s="27">
+      <c r="Q12" s="22">
         <f>P12*K12</f>
         <v>0.96</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="22">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="S12" s="65">
+      <c r="S12" s="56">
         <f>R12*L12</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="T12" s="27">
+      <c r="T12" s="22">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U12" s="65">
+      <c r="U12" s="56">
         <f>T12*M12</f>
         <v>7.0000000000000009</v>
       </c>
-      <c r="V12" s="41"/>
+      <c r="V12" s="36"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="25">
+      <c r="H13" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="20">
         <v>2</v>
       </c>
-      <c r="K13" s="25">
-        <f>J13*5</f>
+      <c r="K13" s="20">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L13" s="25">
-        <f t="shared" si="0"/>
+      <c r="L13" s="20">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M13" s="25">
-        <f t="shared" si="1"/>
+      <c r="M13" s="20">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="22">
         <f>N13*J13</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="P13" s="27">
+      <c r="P13" s="22">
         <v>0.125</v>
       </c>
-      <c r="Q13" s="27">
+      <c r="Q13" s="22">
         <f>P13*K13</f>
         <v>1.25</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="22">
         <v>0.1192</v>
       </c>
-      <c r="S13" s="65">
+      <c r="S13" s="56">
         <f>R13*L13</f>
         <v>5.96</v>
       </c>
-      <c r="T13" s="27">
+      <c r="T13" s="22">
         <v>6.8199999999999997E-2</v>
       </c>
-      <c r="U13" s="65">
+      <c r="U13" s="56">
         <f>T13*M13</f>
         <v>13.639999999999999</v>
       </c>
-      <c r="V13" s="41"/>
+      <c r="V13" s="36"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="56" t="s">
+      <c r="B14" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="I14" s="13" t="s">
+      <c r="H14" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="9">
         <v>1</v>
       </c>
-      <c r="K14" s="14">
-        <f>J14*5</f>
+      <c r="K14" s="9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L14" s="14">
-        <f t="shared" si="0"/>
+      <c r="L14" s="9">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M14" s="14">
-        <f t="shared" si="1"/>
+      <c r="M14" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="10">
         <v>0.1</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="10">
         <f>N14*J14</f>
         <v>0.1</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="10">
         <v>0.1</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="10">
         <f>P14*K14</f>
         <v>0.5</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="10">
         <v>2.4E-2</v>
       </c>
-      <c r="S14" s="54">
+      <c r="S14" s="49">
         <f>R14*L14</f>
         <v>0.6</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="10">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="U14" s="54">
+      <c r="U14" s="49">
         <f>T14*M14</f>
         <v>0.97</v>
       </c>
-      <c r="V14" s="37"/>
+      <c r="V14" s="32"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="58" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" s="17" t="s">
+      <c r="H15" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="13">
         <v>5</v>
       </c>
-      <c r="K15" s="18">
-        <f>J15*5</f>
+      <c r="K15" s="13">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="L15" s="18">
-        <f t="shared" si="0"/>
+      <c r="L15" s="13">
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="M15" s="18">
-        <f t="shared" si="1"/>
+      <c r="M15" s="13">
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="14">
         <v>0.1</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="14">
         <f>N15*J15</f>
         <v>0.5</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="14">
         <v>2.4E-2</v>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="14">
         <f>P15*K15</f>
         <v>0.6</v>
       </c>
-      <c r="R15" s="19">
+      <c r="R15" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="S15" s="42">
+      <c r="S15" s="37">
         <f>R15*L15</f>
         <v>1.2125000000000001</v>
       </c>
-      <c r="T15" s="19">
+      <c r="T15" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="U15" s="42">
+      <c r="U15" s="37">
         <f>T15*M15</f>
         <v>4.8500000000000005</v>
       </c>
-      <c r="V15" s="39"/>
+      <c r="V15" s="34"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" s="44" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I16" s="17" t="s">
+      <c r="H16" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="13">
         <v>1</v>
       </c>
-      <c r="K16" s="18">
-        <f>J16*5</f>
+      <c r="K16" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L16" s="18">
-        <f t="shared" si="0"/>
+      <c r="L16" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M16" s="18">
-        <f t="shared" si="1"/>
+      <c r="M16" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="14">
         <v>0.1</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="14">
         <f>N16*J16</f>
         <v>0.1</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="14">
         <v>0.1</v>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="14">
         <f>P16*K16</f>
         <v>0.5</v>
       </c>
-      <c r="R16" s="19">
+      <c r="R16" s="14">
         <v>2.7E-2</v>
       </c>
-      <c r="S16" s="42">
+      <c r="S16" s="37">
         <f>R16*L16</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="T16" s="19">
+      <c r="T16" s="14">
         <v>1.09E-2</v>
       </c>
-      <c r="U16" s="42">
+      <c r="U16" s="37">
         <f>T16*M16</f>
         <v>1.0900000000000001</v>
       </c>
-      <c r="V16" s="39"/>
+      <c r="V16" s="34"/>
     </row>
     <row r="17" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="44" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I17" s="17" t="s">
+      <c r="H17" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="13">
         <v>2</v>
       </c>
-      <c r="K17" s="18">
-        <f>J17*5</f>
+      <c r="K17" s="13">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L17" s="18">
-        <f t="shared" si="0"/>
+      <c r="L17" s="13">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M17" s="18">
-        <f t="shared" si="1"/>
+      <c r="M17" s="13">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="14">
         <v>0.1</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="14">
         <f>N17*J17</f>
         <v>0.2</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="14">
         <v>0.02</v>
       </c>
-      <c r="Q17" s="19">
+      <c r="Q17" s="14">
         <f>P17*K17</f>
         <v>0.2</v>
       </c>
-      <c r="R17" s="19">
+      <c r="R17" s="14">
         <v>0.02</v>
       </c>
-      <c r="S17" s="42">
+      <c r="S17" s="37">
         <f>R17*L17</f>
         <v>1</v>
       </c>
-      <c r="T17" s="19">
+      <c r="T17" s="14">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="U17" s="42">
+      <c r="U17" s="37">
         <f>T17*M17</f>
         <v>1.6</v>
       </c>
-      <c r="V17" s="39"/>
+      <c r="V17" s="34"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="D18" s="44" t="s">
+      <c r="B18" s="68"/>
+      <c r="C18" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I18" s="17" t="s">
+      <c r="H18" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="13">
         <v>1</v>
       </c>
-      <c r="K18" s="18">
-        <f>J18*5</f>
+      <c r="K18" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L18" s="18">
-        <f t="shared" si="0"/>
+      <c r="L18" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M18" s="18">
-        <f t="shared" si="1"/>
+      <c r="M18" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="14">
         <v>0.1</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="14">
         <f>N18*J18</f>
         <v>0.1</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="14">
         <v>0.1</v>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="14">
         <f>P18*K18</f>
         <v>0.5</v>
       </c>
-      <c r="R18" s="19">
+      <c r="R18" s="14">
         <v>2.4E-2</v>
       </c>
-      <c r="S18" s="42">
+      <c r="S18" s="37">
         <f>R18*L18</f>
         <v>0.6</v>
       </c>
-      <c r="T18" s="19">
+      <c r="T18" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="U18" s="42">
+      <c r="U18" s="37">
         <f>T18*M18</f>
         <v>0.97</v>
       </c>
-      <c r="V18" s="39"/>
+      <c r="V18" s="34"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="58" t="s">
+      <c r="B19" s="68"/>
+      <c r="C19" s="70" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="J19" s="18">
+      <c r="F19" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I19" s="12">
+        <v>57.6</v>
+      </c>
+      <c r="J19" s="13">
         <v>2</v>
       </c>
-      <c r="K19" s="18">
-        <f>J19*5</f>
+      <c r="K19" s="13">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L19" s="18">
-        <f t="shared" si="0"/>
+      <c r="L19" s="13">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M19" s="18">
-        <f t="shared" si="1"/>
+      <c r="M19" s="13">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="14">
         <v>0.1</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="14">
         <f>N19*J19</f>
         <v>0.2</v>
       </c>
-      <c r="P19" s="19">
+      <c r="P19" s="14">
         <v>0.02</v>
       </c>
-      <c r="Q19" s="19">
+      <c r="Q19" s="14">
         <f>P19*K19</f>
         <v>0.2</v>
       </c>
-      <c r="R19" s="19">
+      <c r="R19" s="14">
         <v>0.02</v>
       </c>
-      <c r="S19" s="42">
+      <c r="S19" s="37">
         <f>R19*L19</f>
         <v>1</v>
       </c>
-      <c r="T19" s="19">
+      <c r="T19" s="14">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="U19" s="42">
+      <c r="U19" s="37">
         <f>T19*M19</f>
         <v>1.6199999999999999</v>
       </c>
-      <c r="V19" s="39"/>
+      <c r="V19" s="34"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="J20" s="21">
-        <v>2</v>
-      </c>
-      <c r="K20" s="21">
-        <f>J20*5</f>
-        <v>10</v>
-      </c>
-      <c r="L20" s="21">
+      <c r="H20" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" s="20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="20">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="M20" s="21">
+        <v>5</v>
+      </c>
+      <c r="L20" s="20">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>25</v>
+      </c>
+      <c r="M20" s="20">
+        <f t="shared" si="2"/>
+        <v>100</v>
       </c>
       <c r="N20" s="22">
-        <v>0.1</v>
+        <v>0.96</v>
       </c>
       <c r="O20" s="22">
         <f>N20*J20</f>
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="P20" s="22">
-        <v>4.2000000000000003E-2</v>
+        <v>0.96</v>
       </c>
       <c r="Q20" s="22">
         <f>P20*K20</f>
-        <v>0.42000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="R20" s="22">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="S20" s="55">
+        <v>0.86639999999999995</v>
+      </c>
+      <c r="S20" s="56">
         <f>R20*L20</f>
-        <v>2.1</v>
+        <v>21.66</v>
       </c>
       <c r="T20" s="22">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="U20" s="55">
+        <v>0.75219999999999998</v>
+      </c>
+      <c r="U20" s="56">
         <f>T20*M20</f>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="V20" s="40"/>
+        <v>75.22</v>
+      </c>
+      <c r="V20" s="36"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="J21" s="25">
+        <v>20</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="9">
         <v>1</v>
       </c>
-      <c r="K21" s="25">
-        <f>J21*5</f>
+      <c r="K21" s="9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L21" s="25">
-        <f t="shared" si="0"/>
+      <c r="L21" s="9">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M21" s="25">
-        <f t="shared" si="1"/>
+      <c r="M21" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N21" s="27">
-        <v>0.96</v>
-      </c>
-      <c r="O21" s="27">
+      <c r="N21" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="O21" s="10">
         <f>N21*J21</f>
-        <v>0.96</v>
-      </c>
-      <c r="P21" s="27">
-        <v>0.96</v>
-      </c>
-      <c r="Q21" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="Q21" s="10">
         <f>P21*K21</f>
-        <v>4.8</v>
-      </c>
-      <c r="R21" s="27">
-        <v>0.86639999999999995</v>
-      </c>
-      <c r="S21" s="65">
+        <v>3</v>
+      </c>
+      <c r="R21" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="S21" s="49">
         <f>R21*L21</f>
-        <v>21.66</v>
-      </c>
-      <c r="T21" s="27">
-        <v>0.75219999999999998</v>
-      </c>
-      <c r="U21" s="65">
+        <v>12.5</v>
+      </c>
+      <c r="T21" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="U21" s="49">
         <f>T21*M21</f>
-        <v>75.22</v>
-      </c>
-      <c r="V21" s="41"/>
+        <v>40</v>
+      </c>
+      <c r="V21" s="32"/>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="E22" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="H22" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="16">
         <v>1</v>
       </c>
-      <c r="K22" s="14">
-        <f>J22*5</f>
+      <c r="K22" s="16">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L22" s="14">
-        <f t="shared" si="0"/>
+      <c r="L22" s="16">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M22" s="14">
-        <f t="shared" si="1"/>
+      <c r="M22" s="16">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N22" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="O22" s="15">
+      <c r="N22" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="O22" s="17">
         <f>N22*J22</f>
-        <v>0.6</v>
-      </c>
-      <c r="P22" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="Q22" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="Q22" s="17">
         <f>P22*K22</f>
-        <v>3</v>
-      </c>
-      <c r="R22" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="S22" s="54">
+        <v>4</v>
+      </c>
+      <c r="R22" s="17">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="S22" s="50">
         <f>R22*L22</f>
-        <v>12.5</v>
-      </c>
-      <c r="T22" s="15">
-        <v>0.4</v>
-      </c>
-      <c r="U22" s="54">
+        <v>18.975000000000001</v>
+      </c>
+      <c r="T22" s="17">
+        <v>0.627</v>
+      </c>
+      <c r="U22" s="50">
         <f>T22*M22</f>
-        <v>40</v>
-      </c>
-      <c r="V22" s="37"/>
+        <v>62.7</v>
+      </c>
+      <c r="V22" s="35"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J23" s="9">
         <v>1</v>
       </c>
-      <c r="K23" s="21">
-        <f>J23*5</f>
+      <c r="K23" s="9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L23" s="21">
-        <f t="shared" si="0"/>
+      <c r="L23" s="9">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M23" s="21">
-        <f t="shared" si="1"/>
+      <c r="M23" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N23" s="22">
-        <v>0.8</v>
-      </c>
-      <c r="O23" s="22">
+      <c r="N23" s="23">
+        <v>50.5</v>
+      </c>
+      <c r="O23" s="10">
         <f>N23*J23</f>
-        <v>0.8</v>
-      </c>
-      <c r="P23" s="22">
-        <v>0.8</v>
-      </c>
-      <c r="Q23" s="22">
+        <v>50.5</v>
+      </c>
+      <c r="P23" s="23">
+        <v>50.5</v>
+      </c>
+      <c r="Q23" s="10">
         <f>P23*K23</f>
-        <v>4</v>
-      </c>
-      <c r="R23" s="22">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="S23" s="55">
+        <v>252.5</v>
+      </c>
+      <c r="R23" s="10">
+        <v>50.5</v>
+      </c>
+      <c r="S23" s="49">
         <f>R23*L23</f>
-        <v>18.975000000000001</v>
-      </c>
-      <c r="T23" s="22">
-        <v>0.627</v>
-      </c>
-      <c r="U23" s="55">
+        <v>1262.5</v>
+      </c>
+      <c r="T23" s="10">
+        <v>50.5</v>
+      </c>
+      <c r="U23" s="49">
         <f>T23*M23</f>
-        <v>62.7</v>
-      </c>
-      <c r="V23" s="40"/>
+        <v>5050</v>
+      </c>
+      <c r="V23" s="59" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="E24" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="F24" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="J24" s="14">
+      <c r="H24" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I24" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="J24" s="40">
         <v>1</v>
       </c>
-      <c r="K24" s="14">
-        <f>J24*5</f>
+      <c r="K24" s="40">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="14">
-        <f t="shared" si="0"/>
+      <c r="L24" s="40">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M24" s="14">
-        <f t="shared" si="1"/>
+      <c r="M24" s="40">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N24" s="28">
-        <v>50.5</v>
-      </c>
-      <c r="O24" s="15">
+      <c r="N24" s="41">
+        <v>2.02</v>
+      </c>
+      <c r="O24" s="41">
         <f>N24*J24</f>
-        <v>50.5</v>
-      </c>
-      <c r="P24" s="28">
-        <v>50.5</v>
-      </c>
-      <c r="Q24" s="15">
+        <v>2.02</v>
+      </c>
+      <c r="P24" s="41">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" s="41">
         <f>P24*K24</f>
-        <v>252.5</v>
-      </c>
-      <c r="R24" s="15">
-        <v>50.5</v>
-      </c>
-      <c r="S24" s="54">
+        <v>10.1</v>
+      </c>
+      <c r="R24" s="41">
+        <v>1.74</v>
+      </c>
+      <c r="S24" s="42">
         <f>R24*L24</f>
-        <v>1262.5</v>
-      </c>
-      <c r="T24" s="15">
-        <v>50.5</v>
-      </c>
-      <c r="U24" s="54">
+        <v>43.5</v>
+      </c>
+      <c r="T24" s="41">
+        <v>1.48</v>
+      </c>
+      <c r="U24" s="37">
         <f>T24*M24</f>
-        <v>5050</v>
-      </c>
-      <c r="V24" s="68" t="s">
-        <v>162</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="V24" s="48"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="68"/>
+      <c r="C25" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="E25" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="H25" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J25" s="13">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="13">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M25" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="G25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="45">
-        <v>1</v>
-      </c>
-      <c r="K25" s="45">
-        <f>J25*5</f>
-        <v>5</v>
-      </c>
-      <c r="L25" s="45">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="M25" s="45">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N25" s="46">
-        <v>2.02</v>
-      </c>
-      <c r="O25" s="46">
+      <c r="N25" s="24">
+        <v>10.4</v>
+      </c>
+      <c r="O25" s="14">
         <f>N25*J25</f>
-        <v>2.02</v>
-      </c>
-      <c r="P25" s="46">
-        <v>2.02</v>
-      </c>
-      <c r="Q25" s="46">
+        <v>10.4</v>
+      </c>
+      <c r="P25" s="24">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="Q25" s="14">
         <f>P25*K25</f>
-        <v>10.1</v>
-      </c>
-      <c r="R25" s="46">
-        <v>1.74</v>
-      </c>
-      <c r="S25" s="47">
+        <v>44.75</v>
+      </c>
+      <c r="R25" s="14">
+        <v>8.19</v>
+      </c>
+      <c r="S25" s="37">
         <f>R25*L25</f>
-        <v>43.5</v>
-      </c>
-      <c r="T25" s="46">
-        <v>1.48</v>
-      </c>
-      <c r="U25" s="42">
+        <v>204.75</v>
+      </c>
+      <c r="T25" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="U25" s="37">
         <f>T25*M25</f>
-        <v>148</v>
-      </c>
-      <c r="V25" s="53"/>
+        <v>710</v>
+      </c>
+      <c r="V25" s="34"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>24</v>
-      </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="68"/>
+      <c r="C26" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="E26" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="F26" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H26" s="48" t="s">
+      <c r="H26" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J26" s="13">
+        <v>1</v>
+      </c>
+      <c r="K26" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L26" s="13">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M26" s="13">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="N26" s="14">
+        <v>13.55</v>
+      </c>
+      <c r="O26" s="14">
+        <f>N26*J26</f>
+        <v>13.55</v>
+      </c>
+      <c r="P26" s="14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q26" s="14">
+        <f>P26*K26</f>
+        <v>44</v>
+      </c>
+      <c r="R26" s="14">
+        <v>7.04</v>
+      </c>
+      <c r="S26" s="37">
+        <f>R26*L26</f>
         <v>176</v>
       </c>
-      <c r="I26" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="18">
-        <v>1</v>
-      </c>
-      <c r="K26" s="18">
-        <f>J26*5</f>
-        <v>5</v>
-      </c>
-      <c r="L26" s="18">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="M26" s="18">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N26" s="29">
-        <v>10.4</v>
-      </c>
-      <c r="O26" s="19">
-        <f>N26*J26</f>
-        <v>10.4</v>
-      </c>
-      <c r="P26" s="29">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="Q26" s="19">
-        <f>P26*K26</f>
-        <v>44.75</v>
-      </c>
-      <c r="R26" s="19">
-        <v>8.19</v>
-      </c>
-      <c r="S26" s="42">
-        <f>R26*L26</f>
-        <v>204.75</v>
-      </c>
-      <c r="T26" s="19">
-        <v>7.1</v>
-      </c>
-      <c r="U26" s="42">
+      <c r="T26" s="14">
+        <v>5.6319999999999997</v>
+      </c>
+      <c r="U26" s="37">
         <f>T26*M26</f>
-        <v>710</v>
-      </c>
-      <c r="V26" s="39"/>
+        <v>563.19999999999993</v>
+      </c>
+      <c r="V26" s="58" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="68"/>
+      <c r="C27" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J27" s="13">
+        <v>1</v>
+      </c>
+      <c r="K27" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L27" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="H27" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J27" s="18">
-        <v>1</v>
-      </c>
-      <c r="K27" s="18">
-        <f>J27*5</f>
-        <v>5</v>
-      </c>
-      <c r="L27" s="18">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="M27" s="18">
-        <f t="shared" si="1"/>
+      <c r="M27" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N27" s="19">
-        <v>13.55</v>
-      </c>
-      <c r="O27" s="19">
+      <c r="N27" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="O27" s="14">
         <f>N27*J27</f>
-        <v>13.55</v>
-      </c>
-      <c r="P27" s="19">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="Q27" s="19">
+        <v>0.47</v>
+      </c>
+      <c r="P27" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="Q27" s="14">
         <f>P27*K27</f>
-        <v>44</v>
-      </c>
-      <c r="R27" s="19">
-        <v>7.04</v>
-      </c>
-      <c r="S27" s="42">
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="R27" s="14">
+        <v>0.3508</v>
+      </c>
+      <c r="S27" s="37">
         <f>R27*L27</f>
-        <v>176</v>
-      </c>
-      <c r="T27" s="19">
-        <v>5.6319999999999997</v>
-      </c>
-      <c r="U27" s="42">
+        <v>8.77</v>
+      </c>
+      <c r="T27" s="14">
+        <v>0.26119999999999999</v>
+      </c>
+      <c r="U27" s="37">
         <f>T27*M27</f>
-        <v>563.19999999999993</v>
-      </c>
-      <c r="V27" s="67" t="s">
-        <v>162</v>
+        <v>26.119999999999997</v>
+      </c>
+      <c r="V27" s="58" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="62"/>
-      <c r="C28" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="68"/>
+      <c r="C28" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="F28" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J28" s="18">
+      <c r="H28" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="13">
         <v>1</v>
       </c>
-      <c r="K28" s="18">
-        <f>J28*5</f>
+      <c r="K28" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L28" s="18">
-        <f t="shared" si="0"/>
+      <c r="L28" s="13">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M28" s="18">
-        <f t="shared" si="1"/>
+      <c r="M28" s="13">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N28" s="19">
-        <v>0.47</v>
-      </c>
-      <c r="O28" s="19">
+      <c r="N28" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="O28" s="14">
         <f>N28*J28</f>
-        <v>0.47</v>
-      </c>
-      <c r="P28" s="19">
-        <v>0.47</v>
-      </c>
-      <c r="Q28" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="P28" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="Q28" s="14">
         <f>P28*K28</f>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="R28" s="19">
-        <v>0.3508</v>
-      </c>
-      <c r="S28" s="42">
+        <v>4.5</v>
+      </c>
+      <c r="R28" s="14">
+        <v>0.75280000000000002</v>
+      </c>
+      <c r="S28" s="37">
         <f>R28*L28</f>
-        <v>8.77</v>
-      </c>
-      <c r="T28" s="19">
-        <v>0.26119999999999999</v>
-      </c>
-      <c r="U28" s="42">
+        <v>18.82</v>
+      </c>
+      <c r="T28" s="14">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="U28" s="37">
         <f>T28*M28</f>
-        <v>26.119999999999997</v>
-      </c>
-      <c r="V28" s="67" t="s">
-        <v>150</v>
+        <v>70.5</v>
+      </c>
+      <c r="V28" s="58" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" s="62"/>
-      <c r="C29" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="64"/>
+      <c r="C29" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="E29" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H29" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="18">
+      <c r="F29" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J29" s="16">
         <v>1</v>
       </c>
-      <c r="K29" s="18">
-        <f>J29*5</f>
+      <c r="K29" s="16">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L29" s="18">
-        <f t="shared" si="0"/>
+      <c r="L29" s="16">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M29" s="18">
-        <f t="shared" si="1"/>
+      <c r="M29" s="16">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N29" s="19">
-        <v>0.9</v>
-      </c>
-      <c r="O29" s="19">
+      <c r="N29" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="O29" s="17">
         <f>N29*J29</f>
-        <v>0.9</v>
-      </c>
-      <c r="P29" s="19">
-        <v>0.9</v>
-      </c>
-      <c r="Q29" s="19">
+        <v>0.47</v>
+      </c>
+      <c r="P29" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Q29" s="17">
         <f>P29*K29</f>
-        <v>4.5</v>
-      </c>
-      <c r="R29" s="19">
-        <v>0.75280000000000002</v>
-      </c>
-      <c r="S29" s="42">
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="R29" s="17">
+        <v>0.4244</v>
+      </c>
+      <c r="S29" s="50">
         <f>R29*L29</f>
-        <v>18.82</v>
-      </c>
-      <c r="T29" s="19">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="U29" s="42">
+        <v>10.61</v>
+      </c>
+      <c r="T29" s="17">
+        <v>0.37490000000000001</v>
+      </c>
+      <c r="U29" s="50">
         <f>T29*M29</f>
-        <v>70.5</v>
-      </c>
-      <c r="V29" s="67" t="s">
-        <v>150</v>
-      </c>
+        <v>37.49</v>
+      </c>
+      <c r="V29" s="35"/>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" s="63"/>
-      <c r="C30" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="66" t="s">
-        <v>176</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="J30" s="21">
+        <v>29</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" s="9">
         <v>1</v>
       </c>
-      <c r="K30" s="21">
-        <f>J30*5</f>
+      <c r="K30" s="9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L30" s="21">
-        <f t="shared" si="0"/>
+      <c r="L30" s="9">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M30" s="21">
-        <f t="shared" si="1"/>
+      <c r="M30" s="9">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N30" s="22">
-        <v>0.47</v>
-      </c>
-      <c r="O30" s="22">
+      <c r="N30" s="25">
+        <v>1.27</v>
+      </c>
+      <c r="O30" s="10">
         <f>N30*J30</f>
-        <v>0.47</v>
-      </c>
-      <c r="P30" s="22">
-        <v>0.47</v>
-      </c>
-      <c r="Q30" s="22">
+        <v>1.27</v>
+      </c>
+      <c r="P30" s="25">
+        <v>1.27</v>
+      </c>
+      <c r="Q30" s="10">
         <f>P30*K30</f>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="R30" s="22">
-        <v>0.4244</v>
-      </c>
-      <c r="S30" s="55">
+        <v>6.35</v>
+      </c>
+      <c r="R30" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="S30" s="49">
         <f>R30*L30</f>
-        <v>10.61</v>
-      </c>
-      <c r="T30" s="22">
-        <v>0.37490000000000001</v>
-      </c>
-      <c r="U30" s="55">
+        <v>29.25</v>
+      </c>
+      <c r="T30" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="U30" s="49">
         <f>T30*M30</f>
-        <v>37.49</v>
-      </c>
-      <c r="V30" s="40"/>
+        <v>117</v>
+      </c>
+      <c r="V30" s="32"/>
     </row>
     <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" s="61" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="J31" s="14">
+      <c r="A31" s="60">
+        <v>30</v>
+      </c>
+      <c r="B31" s="64"/>
+      <c r="C31" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="J31" s="16">
         <v>1</v>
       </c>
-      <c r="K31" s="14">
-        <f>J31*5</f>
+      <c r="K31" s="16">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L31" s="14">
-        <f t="shared" si="0"/>
+      <c r="L31" s="16">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="M31" s="14">
-        <f t="shared" si="1"/>
+      <c r="M31" s="16">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N31" s="30">
-        <v>1.27</v>
-      </c>
-      <c r="O31" s="15">
+      <c r="N31" s="16">
+        <v>0.41</v>
+      </c>
+      <c r="O31" s="17">
         <f>N31*J31</f>
-        <v>1.27</v>
-      </c>
-      <c r="P31" s="30">
-        <v>1.27</v>
-      </c>
-      <c r="Q31" s="15">
+        <v>0.41</v>
+      </c>
+      <c r="P31" s="17">
+        <v>0.41</v>
+      </c>
+      <c r="Q31" s="17">
         <f>P31*K31</f>
-        <v>6.35</v>
-      </c>
-      <c r="R31" s="15">
-        <v>1.17</v>
-      </c>
-      <c r="S31" s="54">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="R31" s="17">
+        <v>0.33360000000000001</v>
+      </c>
+      <c r="S31" s="50">
         <f>R31*L31</f>
-        <v>29.25</v>
-      </c>
-      <c r="T31" s="15">
-        <v>1.17</v>
-      </c>
-      <c r="U31" s="54">
+        <v>8.34</v>
+      </c>
+      <c r="T31" s="17">
+        <v>0.27239999999999998</v>
+      </c>
+      <c r="U31" s="50">
         <f>T31*M31</f>
-        <v>117</v>
-      </c>
-      <c r="V31" s="37"/>
+        <v>27.24</v>
+      </c>
+      <c r="V31" s="35"/>
     </row>
-    <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="69">
-        <v>30</v>
-      </c>
-      <c r="B32" s="63"/>
-      <c r="C32" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="J32" s="21">
-        <v>1</v>
-      </c>
-      <c r="K32" s="21">
-        <f>J32*5</f>
-        <v>5</v>
-      </c>
-      <c r="L32" s="21">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="M32" s="21">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N32" s="21">
-        <v>0.41</v>
-      </c>
-      <c r="O32" s="22">
-        <f>N32*J32</f>
-        <v>0.41</v>
-      </c>
-      <c r="P32" s="22">
-        <v>0.41</v>
-      </c>
-      <c r="Q32" s="22">
-        <f>P32*K32</f>
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="R32" s="22">
-        <v>0.33360000000000001</v>
-      </c>
-      <c r="S32" s="55">
-        <f>R32*L32</f>
-        <v>8.34</v>
-      </c>
-      <c r="T32" s="22">
-        <v>0.27239999999999998</v>
-      </c>
-      <c r="U32" s="55">
-        <f>T32*M32</f>
-        <v>27.24</v>
-      </c>
-      <c r="V32" s="40"/>
+    <row r="32" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J32" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="Q32" s="3">
+        <f>SUM(Q3:Q31)</f>
+        <v>402.92000000000013</v>
+      </c>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3">
+        <f>SUM(S3:S31)</f>
+        <v>1889.4874999999997</v>
+      </c>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3">
+        <f>SUM(U3:U31)</f>
+        <v>7123.5899999999992</v>
+      </c>
     </row>
-    <row r="33" spans="10:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J33" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="Q33" s="3">
-        <f>SUM(Q3:Q32)</f>
-        <v>403.34000000000009</v>
-      </c>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3">
-        <f>SUM(S3:S32)</f>
-        <v>1891.5874999999996</v>
-      </c>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3">
-        <f>SUM(U3:U32)</f>
-        <v>7126.9899999999989</v>
-      </c>
-    </row>
-    <row r="34" spans="10:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J34" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="2">
-        <f>SUM(O3:O32)</f>
-        <v>88.503999999999991</v>
-      </c>
-      <c r="Q34" s="4">
-        <f>Q33/5</f>
-        <v>80.668000000000021</v>
-      </c>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4">
-        <f>S33/25</f>
-        <v>75.663499999999985</v>
-      </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4">
-        <f>U33/100</f>
-        <v>71.269899999999993</v>
+    <row r="33" spans="10:21" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="J33" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="K33" s="62"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="2">
+        <f>SUM(O3:O31)</f>
+        <v>88.304000000000002</v>
+      </c>
+      <c r="Q33" s="4">
+        <f>Q32/5</f>
+        <v>80.584000000000032</v>
+      </c>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4">
+        <f>S32/25</f>
+        <v>75.579499999999996</v>
+      </c>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4">
+        <f>U32/100</f>
+        <v>71.235899999999987</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="J32:N32"/>
     <mergeCell ref="J33:N33"/>
-    <mergeCell ref="J34:N34"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B30:B31"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="B3:B8"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B30"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B29"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:M32">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O32">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31993F18-4C5F-4176-9D23-BFACE9C28768}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:U32">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF555A"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BC439CAB-0450-4930-B07F-0CD52FB2A12C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O34:U34">
+  <conditionalFormatting sqref="O33:U33">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -3896,12 +3774,65 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O31">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{31993F18-4C5F-4176-9D23-BFACE9C28768}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:U31">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BC439CAB-0450-4930-B07F-0CD52FB2A12C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:M31">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
   <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{70EE1023-228D-423C-ADF5-29102BB53C0F}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O33:U33</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{31993F18-4C5F-4176-9D23-BFACE9C28768}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -3913,7 +3844,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>O3:O32</xm:sqref>
+          <xm:sqref>O3:O31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BC439CAB-0450-4930-B07F-0CD52FB2A12C}">
@@ -3926,20 +3857,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q3:U32</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70EE1023-228D-423C-ADF5-29102BB53C0F}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>O34:U34</xm:sqref>
+          <xm:sqref>Q3:U31</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/SM_Bottom Board/_BOM/SM_Bottom_Board_DigiKey.xlsx
+++ b/Deliverables/SM_Bottom Board/_BOM/SM_Bottom_Board_DigiKey.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20376"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Github\ColeBenson-SmartMotors\Deliverables\SM_Bottom Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0FAFA8-D593-4D57-B250-FE6A067A5339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4519BEB3-DAB6-4B79-8580-32C2AD1E0579}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5085" yWindow="7680" windowWidth="10335" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1182,6 +1182,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1205,12 +1211,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1522,30 +1522,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="69"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1619,7 +1619,7 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="65" t="s">
         <v>147</v>
       </c>
       <c r="C3" s="51" t="s">
@@ -1662,28 +1662,28 @@
         <v>0.31</v>
       </c>
       <c r="O3" s="10">
-        <f>N3*J3</f>
+        <f t="shared" ref="O3:O31" si="1">N3*J3</f>
         <v>0.31</v>
       </c>
       <c r="P3" s="10">
         <v>0.31</v>
       </c>
       <c r="Q3" s="10">
-        <f>P3*K3</f>
+        <f t="shared" ref="Q3:Q31" si="2">P3*K3</f>
         <v>1.55</v>
       </c>
       <c r="R3" s="10">
         <v>0.21299999999999999</v>
       </c>
       <c r="S3" s="49">
-        <f>R3*L3</f>
+        <f t="shared" ref="S3:S31" si="3">R3*L3</f>
         <v>5.3250000000000002</v>
       </c>
       <c r="T3" s="10">
         <v>0.12039999999999999</v>
       </c>
       <c r="U3" s="49">
-        <f>T3*M3</f>
+        <f t="shared" ref="U3:U31" si="4">T3*M3</f>
         <v>12.04</v>
       </c>
       <c r="V3" s="32"/>
@@ -1692,8 +1692,8 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="70"/>
+      <c r="C4" s="61" t="s">
         <v>160</v>
       </c>
       <c r="D4" s="45" t="s">
@@ -1722,39 +1722,39 @@
         <v>100</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" ref="L4:L31" si="1">J4*25</f>
+        <f t="shared" ref="L4:L31" si="5">J4*25</f>
         <v>500</v>
       </c>
       <c r="M4" s="13">
-        <f t="shared" ref="M4:M31" si="2">J4*100</f>
+        <f t="shared" ref="M4:M31" si="6">J4*100</f>
         <v>2000</v>
       </c>
       <c r="N4" s="27">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="O4" s="27">
-        <f>N4*J4</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
       <c r="P4" s="27">
         <v>2.1399999999999999E-2</v>
       </c>
       <c r="Q4" s="27">
-        <f>P4*K4</f>
+        <f t="shared" si="2"/>
         <v>2.1399999999999997</v>
       </c>
       <c r="R4" s="27">
         <v>1.5259999999999999E-2</v>
       </c>
       <c r="S4" s="37">
-        <f>R4*L4</f>
+        <f t="shared" si="3"/>
         <v>7.63</v>
       </c>
       <c r="T4" s="27">
         <v>1.1990000000000001E-2</v>
       </c>
       <c r="U4" s="37">
-        <f>T4*M4</f>
+        <f t="shared" si="4"/>
         <v>23.98</v>
       </c>
       <c r="V4" s="33"/>
@@ -1763,7 +1763,7 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="70"/>
       <c r="C5" s="52" t="s">
         <v>13</v>
       </c>
@@ -1793,39 +1793,39 @@
         <v>5</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M5" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N5" s="14">
         <v>0.79</v>
       </c>
       <c r="O5" s="14">
-        <f>N5*J5</f>
+        <f t="shared" si="1"/>
         <v>0.79</v>
       </c>
       <c r="P5" s="14">
         <v>0.79</v>
       </c>
       <c r="Q5" s="14">
-        <f>P5*K5</f>
+        <f t="shared" si="2"/>
         <v>3.95</v>
       </c>
       <c r="R5" s="14">
         <v>0.55800000000000005</v>
       </c>
       <c r="S5" s="37">
-        <f>R5*L5</f>
+        <f t="shared" si="3"/>
         <v>13.950000000000001</v>
       </c>
       <c r="T5" s="14">
         <v>0.36770000000000003</v>
       </c>
       <c r="U5" s="37">
-        <f>T5*M5</f>
+        <f t="shared" si="4"/>
         <v>36.770000000000003</v>
       </c>
       <c r="V5" s="34"/>
@@ -1834,7 +1834,7 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="68"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="52" t="s">
         <v>163</v>
       </c>
@@ -1864,39 +1864,39 @@
         <v>10</v>
       </c>
       <c r="L6" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="M6" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N6" s="14">
         <v>0.21</v>
       </c>
       <c r="O6" s="14">
-        <f>N6*J6</f>
+        <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
       <c r="P6" s="14">
         <v>0.14299999999999999</v>
       </c>
       <c r="Q6" s="14">
-        <f>P6*K6</f>
+        <f t="shared" si="2"/>
         <v>1.43</v>
       </c>
       <c r="R6" s="14">
         <v>8.5599999999999996E-2</v>
       </c>
       <c r="S6" s="37">
-        <f>R6*L6</f>
+        <f t="shared" si="3"/>
         <v>4.2799999999999994</v>
       </c>
       <c r="T6" s="14">
         <v>7.2400000000000006E-2</v>
       </c>
       <c r="U6" s="37">
-        <f>T6*M6</f>
+        <f t="shared" si="4"/>
         <v>14.48</v>
       </c>
       <c r="V6" s="34"/>
@@ -1905,7 +1905,7 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="68"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="52" t="s">
         <v>23</v>
       </c>
@@ -1935,39 +1935,39 @@
         <v>20</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="M7" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>400</v>
       </c>
       <c r="N7" s="14">
         <v>0.11</v>
       </c>
       <c r="O7" s="14">
-        <f>N7*J7</f>
+        <f t="shared" si="1"/>
         <v>0.44</v>
       </c>
       <c r="P7" s="14">
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="Q7" s="14">
-        <f>P7*K7</f>
+        <f t="shared" si="2"/>
         <v>1.58</v>
       </c>
       <c r="R7" s="14">
         <v>3.5400000000000001E-2</v>
       </c>
       <c r="S7" s="37">
-        <f>R7*L7</f>
+        <f t="shared" si="3"/>
         <v>3.54</v>
       </c>
       <c r="T7" s="14">
         <v>3.5400000000000001E-2</v>
       </c>
       <c r="U7" s="37">
-        <f>T7*M7</f>
+        <f t="shared" si="4"/>
         <v>14.16</v>
       </c>
       <c r="V7" s="34"/>
@@ -1976,7 +1976,7 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="64"/>
+      <c r="B8" s="66"/>
       <c r="C8" s="53" t="s">
         <v>28</v>
       </c>
@@ -2006,39 +2006,39 @@
         <v>5</v>
       </c>
       <c r="L8" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M8" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N8" s="17">
         <v>0.35</v>
       </c>
       <c r="O8" s="17">
-        <f>N8*J8</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
       <c r="P8" s="17">
         <v>0.35</v>
       </c>
       <c r="Q8" s="17">
-        <f>P8*K8</f>
+        <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
       <c r="R8" s="17">
         <v>0.24199999999999999</v>
       </c>
       <c r="S8" s="50">
-        <f>R8*L8</f>
+        <f t="shared" si="3"/>
         <v>6.05</v>
       </c>
       <c r="T8" s="17">
         <v>0.1368</v>
       </c>
       <c r="U8" s="50">
-        <f>T8*M8</f>
+        <f t="shared" si="4"/>
         <v>13.68</v>
       </c>
       <c r="V8" s="35"/>
@@ -2047,7 +2047,7 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="65" t="s">
         <v>148</v>
       </c>
       <c r="C9" s="51" t="s">
@@ -2079,39 +2079,39 @@
         <v>10</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N9" s="18">
         <v>0.13100000000000001</v>
       </c>
       <c r="O9" s="10">
-        <f>N9*J9</f>
+        <f t="shared" si="1"/>
         <v>0.26200000000000001</v>
       </c>
       <c r="P9" s="18">
         <v>0.13100000000000001</v>
       </c>
       <c r="Q9" s="10">
-        <f>P9*K9</f>
+        <f t="shared" si="2"/>
         <v>1.31</v>
       </c>
       <c r="R9" s="10">
         <v>0.1048</v>
       </c>
       <c r="S9" s="49">
-        <f>R9*L9</f>
+        <f t="shared" si="3"/>
         <v>5.24</v>
       </c>
       <c r="T9" s="10">
         <v>0.1</v>
       </c>
       <c r="U9" s="49">
-        <f>T9*M9</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="V9" s="59" t="s">
@@ -2122,7 +2122,7 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="52" t="s">
         <v>37</v>
       </c>
@@ -2152,39 +2152,39 @@
         <v>5</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M10" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N10" s="14">
         <v>0.38</v>
       </c>
       <c r="O10" s="14">
-        <f>N10*J10</f>
+        <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
       <c r="P10" s="14">
         <v>0.38</v>
       </c>
       <c r="Q10" s="14">
-        <f>P10*K10</f>
+        <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
       <c r="R10" s="14">
         <v>0.28499999999999998</v>
       </c>
       <c r="S10" s="37">
-        <f>R10*L10</f>
+        <f t="shared" si="3"/>
         <v>7.1249999999999991</v>
       </c>
       <c r="T10" s="14">
         <v>0.1613</v>
       </c>
       <c r="U10" s="37">
-        <f>T10*M10</f>
+        <f t="shared" si="4"/>
         <v>16.13</v>
       </c>
       <c r="V10" s="34"/>
@@ -2193,7 +2193,7 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="64"/>
+      <c r="B11" s="66"/>
       <c r="C11" s="53" t="s">
         <v>50</v>
       </c>
@@ -2223,39 +2223,39 @@
         <v>5</v>
       </c>
       <c r="L11" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M11" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N11" s="17">
         <v>0.37</v>
       </c>
       <c r="O11" s="17">
-        <f>N11*J11</f>
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
       <c r="P11" s="17">
         <v>0.37</v>
       </c>
       <c r="Q11" s="17">
-        <f>P11*K11</f>
+        <f t="shared" si="2"/>
         <v>1.85</v>
       </c>
       <c r="R11" s="17">
         <v>0.29299999999999998</v>
       </c>
       <c r="S11" s="50">
-        <f>R11*L11</f>
+        <f t="shared" si="3"/>
         <v>7.3249999999999993</v>
       </c>
       <c r="T11" s="17">
         <v>0.13139999999999999</v>
       </c>
       <c r="U11" s="50">
-        <f>T11*M11</f>
+        <f t="shared" si="4"/>
         <v>13.139999999999999</v>
       </c>
       <c r="V11" s="35"/>
@@ -2294,39 +2294,39 @@
         <v>5</v>
       </c>
       <c r="L12" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M12" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N12" s="21">
         <v>0.192</v>
       </c>
       <c r="O12" s="22">
-        <f>N12*J12</f>
+        <f t="shared" si="1"/>
         <v>0.192</v>
       </c>
       <c r="P12" s="21">
         <v>0.192</v>
       </c>
       <c r="Q12" s="22">
-        <f>P12*K12</f>
+        <f t="shared" si="2"/>
         <v>0.96</v>
       </c>
       <c r="R12" s="22">
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="S12" s="56">
-        <f>R12*L12</f>
+        <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="T12" s="22">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="U12" s="56">
-        <f>T12*M12</f>
+        <f t="shared" si="4"/>
         <v>7.0000000000000009</v>
       </c>
       <c r="V12" s="36"/>
@@ -2365,39 +2365,39 @@
         <v>10</v>
       </c>
       <c r="L13" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="M13" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N13" s="22">
         <v>0.14000000000000001</v>
       </c>
       <c r="O13" s="22">
-        <f>N13*J13</f>
+        <f t="shared" si="1"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="P13" s="22">
         <v>0.125</v>
       </c>
       <c r="Q13" s="22">
-        <f>P13*K13</f>
+        <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
       <c r="R13" s="22">
         <v>0.1192</v>
       </c>
       <c r="S13" s="56">
-        <f>R13*L13</f>
+        <f t="shared" si="3"/>
         <v>5.96</v>
       </c>
       <c r="T13" s="22">
         <v>6.8199999999999997E-2</v>
       </c>
       <c r="U13" s="56">
-        <f>T13*M13</f>
+        <f t="shared" si="4"/>
         <v>13.639999999999999</v>
       </c>
       <c r="V13" s="36"/>
@@ -2406,7 +2406,7 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="65" t="s">
         <v>150</v>
       </c>
       <c r="C14" s="51" t="s">
@@ -2438,39 +2438,39 @@
         <v>5</v>
       </c>
       <c r="L14" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M14" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N14" s="10">
         <v>0.1</v>
       </c>
       <c r="O14" s="10">
-        <f>N14*J14</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="P14" s="10">
         <v>0.1</v>
       </c>
       <c r="Q14" s="10">
-        <f>P14*K14</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="R14" s="10">
         <v>2.4E-2</v>
       </c>
       <c r="S14" s="49">
-        <f>R14*L14</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="T14" s="10">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="U14" s="49">
-        <f>T14*M14</f>
+        <f t="shared" si="4"/>
         <v>0.97</v>
       </c>
       <c r="V14" s="32"/>
@@ -2479,7 +2479,7 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="68"/>
+      <c r="B15" s="70"/>
       <c r="C15" s="52" t="s">
         <v>70</v>
       </c>
@@ -2509,39 +2509,39 @@
         <v>25</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>125</v>
       </c>
       <c r="M15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N15" s="14">
         <v>0.1</v>
       </c>
       <c r="O15" s="14">
-        <f>N15*J15</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P15" s="14">
         <v>2.4E-2</v>
       </c>
       <c r="Q15" s="14">
-        <f>P15*K15</f>
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="R15" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="S15" s="37">
-        <f>R15*L15</f>
+        <f t="shared" si="3"/>
         <v>1.2125000000000001</v>
       </c>
       <c r="T15" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="U15" s="37">
-        <f>T15*M15</f>
+        <f t="shared" si="4"/>
         <v>4.8500000000000005</v>
       </c>
       <c r="V15" s="34"/>
@@ -2550,7 +2550,7 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="52" t="s">
         <v>172</v>
       </c>
@@ -2580,39 +2580,39 @@
         <v>5</v>
       </c>
       <c r="L16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N16" s="14">
         <v>0.1</v>
       </c>
       <c r="O16" s="14">
-        <f>N16*J16</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="P16" s="14">
         <v>0.1</v>
       </c>
       <c r="Q16" s="14">
-        <f>P16*K16</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="R16" s="14">
         <v>2.7E-2</v>
       </c>
       <c r="S16" s="37">
-        <f>R16*L16</f>
+        <f t="shared" si="3"/>
         <v>0.67500000000000004</v>
       </c>
       <c r="T16" s="14">
         <v>1.09E-2</v>
       </c>
       <c r="U16" s="37">
-        <f>T16*M16</f>
+        <f t="shared" si="4"/>
         <v>1.0900000000000001</v>
       </c>
       <c r="V16" s="34"/>
@@ -2621,7 +2621,7 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="68"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="52" t="s">
         <v>170</v>
       </c>
@@ -2651,39 +2651,39 @@
         <v>10</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="M17" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N17" s="14">
         <v>0.1</v>
       </c>
       <c r="O17" s="14">
-        <f>N17*J17</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="P17" s="14">
         <v>0.02</v>
       </c>
       <c r="Q17" s="14">
-        <f>P17*K17</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="R17" s="14">
         <v>0.02</v>
       </c>
       <c r="S17" s="37">
-        <f>R17*L17</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T17" s="14">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="U17" s="37">
-        <f>T17*M17</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="V17" s="34"/>
@@ -2692,7 +2692,7 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="68"/>
+      <c r="B18" s="70"/>
       <c r="C18" s="52" t="s">
         <v>171</v>
       </c>
@@ -2722,39 +2722,39 @@
         <v>5</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M18" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N18" s="14">
         <v>0.1</v>
       </c>
       <c r="O18" s="14">
-        <f>N18*J18</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="P18" s="14">
         <v>0.1</v>
       </c>
       <c r="Q18" s="14">
-        <f>P18*K18</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="R18" s="14">
         <v>2.4E-2</v>
       </c>
       <c r="S18" s="37">
-        <f>R18*L18</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="T18" s="14">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="U18" s="37">
-        <f>T18*M18</f>
+        <f t="shared" si="4"/>
         <v>0.97</v>
       </c>
       <c r="V18" s="34"/>
@@ -2763,8 +2763,8 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="70" t="s">
+      <c r="B19" s="70"/>
+      <c r="C19" s="62" t="s">
         <v>182</v>
       </c>
       <c r="D19" s="39" t="s">
@@ -2793,39 +2793,39 @@
         <v>10</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="M19" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N19" s="14">
         <v>0.1</v>
       </c>
       <c r="O19" s="14">
-        <f>N19*J19</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="P19" s="14">
         <v>0.02</v>
       </c>
       <c r="Q19" s="14">
-        <f>P19*K19</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="R19" s="14">
         <v>0.02</v>
       </c>
       <c r="S19" s="37">
-        <f>R19*L19</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T19" s="14">
         <v>8.0999999999999996E-3</v>
       </c>
       <c r="U19" s="37">
-        <f>T19*M19</f>
+        <f t="shared" si="4"/>
         <v>1.6199999999999999</v>
       </c>
       <c r="V19" s="34"/>
@@ -2866,39 +2866,39 @@
         <v>5</v>
       </c>
       <c r="L20" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M20" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N20" s="22">
         <v>0.96</v>
       </c>
       <c r="O20" s="22">
-        <f>N20*J20</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
       <c r="P20" s="22">
         <v>0.96</v>
       </c>
       <c r="Q20" s="22">
-        <f>P20*K20</f>
+        <f t="shared" si="2"/>
         <v>4.8</v>
       </c>
       <c r="R20" s="22">
         <v>0.86639999999999995</v>
       </c>
       <c r="S20" s="56">
-        <f>R20*L20</f>
+        <f t="shared" si="3"/>
         <v>21.66</v>
       </c>
       <c r="T20" s="22">
         <v>0.75219999999999998</v>
       </c>
       <c r="U20" s="56">
-        <f>T20*M20</f>
+        <f t="shared" si="4"/>
         <v>75.22</v>
       </c>
       <c r="V20" s="36"/>
@@ -2907,7 +2907,7 @@
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="65" t="s">
         <v>152</v>
       </c>
       <c r="C21" s="51" t="s">
@@ -2939,39 +2939,39 @@
         <v>5</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N21" s="10">
         <v>0.6</v>
       </c>
       <c r="O21" s="10">
-        <f>N21*J21</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="P21" s="10">
         <v>0.6</v>
       </c>
       <c r="Q21" s="10">
-        <f>P21*K21</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="R21" s="10">
         <v>0.5</v>
       </c>
       <c r="S21" s="49">
-        <f>R21*L21</f>
+        <f t="shared" si="3"/>
         <v>12.5</v>
       </c>
       <c r="T21" s="10">
         <v>0.4</v>
       </c>
       <c r="U21" s="49">
-        <f>T21*M21</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="V21" s="32"/>
@@ -2980,7 +2980,7 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="64"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="53" t="s">
         <v>128</v>
       </c>
@@ -3010,39 +3010,39 @@
         <v>5</v>
       </c>
       <c r="L22" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M22" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N22" s="17">
         <v>0.8</v>
       </c>
       <c r="O22" s="17">
-        <f>N22*J22</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="P22" s="17">
         <v>0.8</v>
       </c>
       <c r="Q22" s="17">
-        <f>P22*K22</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="R22" s="17">
         <v>0.75900000000000001</v>
       </c>
       <c r="S22" s="50">
-        <f>R22*L22</f>
+        <f t="shared" si="3"/>
         <v>18.975000000000001</v>
       </c>
       <c r="T22" s="17">
         <v>0.627</v>
       </c>
       <c r="U22" s="50">
-        <f>T22*M22</f>
+        <f t="shared" si="4"/>
         <v>62.7</v>
       </c>
       <c r="V22" s="35"/>
@@ -3051,7 +3051,7 @@
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="65" t="s">
         <v>153</v>
       </c>
       <c r="C23" s="51" t="s">
@@ -3083,39 +3083,39 @@
         <v>5</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N23" s="23">
         <v>50.5</v>
       </c>
       <c r="O23" s="10">
-        <f>N23*J23</f>
+        <f t="shared" si="1"/>
         <v>50.5</v>
       </c>
       <c r="P23" s="23">
         <v>50.5</v>
       </c>
       <c r="Q23" s="10">
-        <f>P23*K23</f>
+        <f t="shared" si="2"/>
         <v>252.5</v>
       </c>
       <c r="R23" s="10">
         <v>50.5</v>
       </c>
       <c r="S23" s="49">
-        <f>R23*L23</f>
+        <f t="shared" si="3"/>
         <v>1262.5</v>
       </c>
       <c r="T23" s="10">
         <v>50.5</v>
       </c>
       <c r="U23" s="49">
-        <f>T23*M23</f>
+        <f t="shared" si="4"/>
         <v>5050</v>
       </c>
       <c r="V23" s="59" t="s">
@@ -3126,7 +3126,7 @@
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="68"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="54" t="s">
         <v>95</v>
       </c>
@@ -3156,39 +3156,39 @@
         <v>5</v>
       </c>
       <c r="L24" s="40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M24" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N24" s="41">
         <v>2.02</v>
       </c>
       <c r="O24" s="41">
-        <f>N24*J24</f>
+        <f t="shared" si="1"/>
         <v>2.02</v>
       </c>
       <c r="P24" s="41">
         <v>2.02</v>
       </c>
       <c r="Q24" s="41">
-        <f>P24*K24</f>
+        <f t="shared" si="2"/>
         <v>10.1</v>
       </c>
       <c r="R24" s="41">
         <v>1.74</v>
       </c>
       <c r="S24" s="42">
-        <f>R24*L24</f>
+        <f t="shared" si="3"/>
         <v>43.5</v>
       </c>
       <c r="T24" s="41">
         <v>1.48</v>
       </c>
       <c r="U24" s="37">
-        <f>T24*M24</f>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="V24" s="48"/>
@@ -3197,7 +3197,7 @@
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="68"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="52" t="s">
         <v>100</v>
       </c>
@@ -3227,39 +3227,39 @@
         <v>5</v>
       </c>
       <c r="L25" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M25" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N25" s="24">
         <v>10.4</v>
       </c>
       <c r="O25" s="14">
-        <f>N25*J25</f>
+        <f t="shared" si="1"/>
         <v>10.4</v>
       </c>
       <c r="P25" s="24">
         <v>8.9499999999999993</v>
       </c>
       <c r="Q25" s="14">
-        <f>P25*K25</f>
+        <f t="shared" si="2"/>
         <v>44.75</v>
       </c>
       <c r="R25" s="14">
         <v>8.19</v>
       </c>
       <c r="S25" s="37">
-        <f>R25*L25</f>
+        <f t="shared" si="3"/>
         <v>204.75</v>
       </c>
       <c r="T25" s="14">
         <v>7.1</v>
       </c>
       <c r="U25" s="37">
-        <f>T25*M25</f>
+        <f t="shared" si="4"/>
         <v>710</v>
       </c>
       <c r="V25" s="34"/>
@@ -3268,7 +3268,7 @@
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="68"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="52" t="s">
         <v>105</v>
       </c>
@@ -3298,39 +3298,39 @@
         <v>5</v>
       </c>
       <c r="L26" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N26" s="14">
         <v>13.55</v>
       </c>
       <c r="O26" s="14">
-        <f>N26*J26</f>
+        <f t="shared" si="1"/>
         <v>13.55</v>
       </c>
       <c r="P26" s="14">
         <v>8.8000000000000007</v>
       </c>
       <c r="Q26" s="14">
-        <f>P26*K26</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="R26" s="14">
         <v>7.04</v>
       </c>
       <c r="S26" s="37">
-        <f>R26*L26</f>
+        <f t="shared" si="3"/>
         <v>176</v>
       </c>
       <c r="T26" s="14">
         <v>5.6319999999999997</v>
       </c>
       <c r="U26" s="37">
-        <f>T26*M26</f>
+        <f t="shared" si="4"/>
         <v>563.19999999999993</v>
       </c>
       <c r="V26" s="58" t="s">
@@ -3341,7 +3341,7 @@
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="68"/>
+      <c r="B27" s="70"/>
       <c r="C27" s="52" t="s">
         <v>110</v>
       </c>
@@ -3371,39 +3371,39 @@
         <v>5</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M27" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N27" s="14">
         <v>0.47</v>
       </c>
       <c r="O27" s="14">
-        <f>N27*J27</f>
+        <f t="shared" si="1"/>
         <v>0.47</v>
       </c>
       <c r="P27" s="14">
         <v>0.47</v>
       </c>
       <c r="Q27" s="14">
-        <f>P27*K27</f>
+        <f t="shared" si="2"/>
         <v>2.3499999999999996</v>
       </c>
       <c r="R27" s="14">
         <v>0.3508</v>
       </c>
       <c r="S27" s="37">
-        <f>R27*L27</f>
+        <f t="shared" si="3"/>
         <v>8.77</v>
       </c>
       <c r="T27" s="14">
         <v>0.26119999999999999</v>
       </c>
       <c r="U27" s="37">
-        <f>T27*M27</f>
+        <f t="shared" si="4"/>
         <v>26.119999999999997</v>
       </c>
       <c r="V27" s="58" t="s">
@@ -3414,7 +3414,7 @@
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="68"/>
+      <c r="B28" s="70"/>
       <c r="C28" s="52" t="s">
         <v>114</v>
       </c>
@@ -3444,39 +3444,39 @@
         <v>5</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M28" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N28" s="14">
         <v>0.9</v>
       </c>
       <c r="O28" s="14">
-        <f>N28*J28</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="P28" s="14">
         <v>0.9</v>
       </c>
       <c r="Q28" s="14">
-        <f>P28*K28</f>
+        <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
       <c r="R28" s="14">
         <v>0.75280000000000002</v>
       </c>
       <c r="S28" s="37">
-        <f>R28*L28</f>
+        <f t="shared" si="3"/>
         <v>18.82</v>
       </c>
       <c r="T28" s="14">
         <v>0.70499999999999996</v>
       </c>
       <c r="U28" s="37">
-        <f>T28*M28</f>
+        <f t="shared" si="4"/>
         <v>70.5</v>
       </c>
       <c r="V28" s="58" t="s">
@@ -3487,7 +3487,7 @@
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="64"/>
+      <c r="B29" s="66"/>
       <c r="C29" s="53" t="s">
         <v>119</v>
       </c>
@@ -3517,39 +3517,39 @@
         <v>5</v>
       </c>
       <c r="L29" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M29" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N29" s="17">
         <v>0.47</v>
       </c>
       <c r="O29" s="17">
-        <f>N29*J29</f>
+        <f t="shared" si="1"/>
         <v>0.47</v>
       </c>
       <c r="P29" s="17">
         <v>0.47</v>
       </c>
       <c r="Q29" s="17">
-        <f>P29*K29</f>
+        <f t="shared" si="2"/>
         <v>2.3499999999999996</v>
       </c>
       <c r="R29" s="17">
         <v>0.4244</v>
       </c>
       <c r="S29" s="50">
-        <f>R29*L29</f>
+        <f t="shared" si="3"/>
         <v>10.61</v>
       </c>
       <c r="T29" s="17">
         <v>0.37490000000000001</v>
       </c>
       <c r="U29" s="50">
-        <f>T29*M29</f>
+        <f t="shared" si="4"/>
         <v>37.49</v>
       </c>
       <c r="V29" s="35"/>
@@ -3558,7 +3558,7 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="65" t="s">
         <v>154</v>
       </c>
       <c r="C30" s="51" t="s">
@@ -3590,39 +3590,39 @@
         <v>5</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N30" s="25">
         <v>1.27</v>
       </c>
       <c r="O30" s="10">
-        <f>N30*J30</f>
+        <f t="shared" si="1"/>
         <v>1.27</v>
       </c>
       <c r="P30" s="25">
         <v>1.27</v>
       </c>
       <c r="Q30" s="10">
-        <f>P30*K30</f>
+        <f t="shared" si="2"/>
         <v>6.35</v>
       </c>
       <c r="R30" s="10">
         <v>1.17</v>
       </c>
       <c r="S30" s="49">
-        <f>R30*L30</f>
+        <f t="shared" si="3"/>
         <v>29.25</v>
       </c>
       <c r="T30" s="10">
         <v>1.17</v>
       </c>
       <c r="U30" s="49">
-        <f>T30*M30</f>
+        <f t="shared" si="4"/>
         <v>117</v>
       </c>
       <c r="V30" s="32"/>
@@ -3631,7 +3631,7 @@
       <c r="A31" s="60">
         <v>30</v>
       </c>
-      <c r="B31" s="64"/>
+      <c r="B31" s="66"/>
       <c r="C31" s="53" t="s">
         <v>55</v>
       </c>
@@ -3661,51 +3661,51 @@
         <v>5</v>
       </c>
       <c r="L31" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="M31" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="N31" s="16">
         <v>0.41</v>
       </c>
       <c r="O31" s="17">
-        <f>N31*J31</f>
+        <f t="shared" si="1"/>
         <v>0.41</v>
       </c>
       <c r="P31" s="17">
         <v>0.41</v>
       </c>
       <c r="Q31" s="17">
-        <f>P31*K31</f>
+        <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
       <c r="R31" s="17">
         <v>0.33360000000000001</v>
       </c>
       <c r="S31" s="50">
-        <f>R31*L31</f>
+        <f t="shared" si="3"/>
         <v>8.34</v>
       </c>
       <c r="T31" s="17">
         <v>0.27239999999999998</v>
       </c>
       <c r="U31" s="50">
-        <f>T31*M31</f>
+        <f t="shared" si="4"/>
         <v>27.24</v>
       </c>
       <c r="V31" s="35"/>
     </row>
     <row r="32" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J32" s="61" t="s">
+      <c r="J32" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
       <c r="Q32" s="3">
         <f>SUM(Q3:Q31)</f>
         <v>402.92000000000013</v>
@@ -3722,13 +3722,13 @@
       </c>
     </row>
     <row r="33" spans="10:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J33" s="62" t="s">
+      <c r="J33" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
-      <c r="N33" s="62"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
       <c r="O33" s="2">
         <f>SUM(O3:O31)</f>
         <v>88.304000000000002</v>
